--- a/artfynd/A 30156-2022 artfynd.xlsx
+++ b/artfynd/A 30156-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30156-2022 artfynd.xlsx
+++ b/artfynd/A 30156-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6767,6 +6767,122 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>118121319</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97744</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>504</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gucku viksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>695984</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6637498</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>ca 200</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Olle Amcoff</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Olle Amcoff</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30156-2022 artfynd.xlsx
+++ b/artfynd/A 30156-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>53976134</v>
+        <v>73112909</v>
       </c>
       <c r="B2" t="n">
-        <v>108194</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>150</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björknäs SO, Upl</t>
+          <t>Björknäs SO om, Erken, Lohärad, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696032.210440265</v>
+        <v>696130</v>
       </c>
       <c r="R2" t="n">
-        <v>6637537.379643583</v>
+        <v>6637467</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,22 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Inventering tillsammans med Kristoffer Stighäll och Birgitta Wasstorp.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,65 +773,56 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Örtrik gammal granskog med stort lövinslag.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Christoffer Hallbäck</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Christoffer Hallbäck</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73099226</v>
+        <v>73120808</v>
       </c>
       <c r="B3" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1988</v>
+        <v>150</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -856,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696037.3541234477</v>
+        <v>696037</v>
       </c>
       <c r="R3" t="n">
-        <v>6637487.782187801</v>
+        <v>6637488</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -886,22 +867,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spridd i området. Flera utmed stigar och stigkors.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,63 +905,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73088656</v>
+        <v>79969277</v>
       </c>
       <c r="B4" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>150</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696037.3541234477</v>
+        <v>696109</v>
       </c>
       <c r="R4" t="n">
-        <v>6637487.782187801</v>
+        <v>6637509</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,27 +981,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>minst. Väl spridd.</t>
+          <t>Gammal kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,75 +1007,71 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73088665</v>
+        <v>79970784</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grangråticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Boletopsis leucomelaena</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Pers.) Fayod</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696037.3541234477</v>
+        <v>696075</v>
       </c>
       <c r="R5" t="n">
-        <v>6637487.782187801</v>
+        <v>6637540</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1137,27 +1095,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>minst. Väl spridd.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,27 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73088664</v>
+        <v>6759043</v>
       </c>
       <c r="B6" t="n">
-        <v>90649</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,39 +1144,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4363</v>
+        <v>504</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björknäs, SO om, Upl</t>
+          <t>Björknäs (*gk* /stjälk/), Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696037.3541234477</v>
+        <v>695966</v>
       </c>
       <c r="R6" t="n">
-        <v>6637487.782187801</v>
+        <v>6637523</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,24 +1196,24 @@
           <t>Lohärad</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>AB-Nor-0634-biogeo</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1975-07-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1975-07-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>50 ex / 4 km NV om Lohärad kyrka, 100 m SO om s i Björknäs., 6637455, 1650955, 100 m /</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,34 +1222,32 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>AB-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via AB-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73088925</v>
+        <v>6764842</v>
       </c>
       <c r="B7" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,47 +1255,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>504</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björknäs, SO om, Upl</t>
+          <t>Björklund 300 m V (*gk* /stjälk/), Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696037.3541234477</v>
+        <v>696093</v>
       </c>
       <c r="R7" t="n">
-        <v>6637487.782187801</v>
+        <v>6637409</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1378,29 +1307,24 @@
           <t>Lohärad</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>AB-Nor-0635</t>
+        </is>
+      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-10-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-10-26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Minst. Väl spridd.</t>
+          <t>Objekt 15:1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,34 +1333,32 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>AB-län Floraväktarna</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Stefan Eklund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73099330</v>
+        <v>53976133</v>
       </c>
       <c r="B8" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1444,47 +1366,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>504</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björknäs, SO om, Upl</t>
+          <t>Björknäs SO, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696037.3541234477</v>
+        <v>695966</v>
       </c>
       <c r="R8" t="n">
-        <v>6637487.782187801</v>
+        <v>6637510</v>
       </c>
       <c r="S8" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1508,22 +1434,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ett bestånd ca 4 x 2 m.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1532,34 +1453,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Örtrik gammal granskog med stort lövinslag.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73088914</v>
+        <v>79970656</v>
       </c>
       <c r="B9" t="n">
-        <v>86788</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,47 +1487,41 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4566</v>
+        <v>504</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dofttråding</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Inosperma bongardii</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Weinm.) Matheny &amp; Estev-Rav.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696037.3541234477</v>
+        <v>695975</v>
       </c>
       <c r="R9" t="n">
-        <v>6637487.782187801</v>
+        <v>6637513</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1631,27 +1545,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Områdets N del. I svacka. Rik markväxtlighet med kransmossa, blåsippa och harsyra.</t>
+          <t>Många exemplar på en yta av ca 2x3m. Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1667,67 +1571,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>73099153</v>
+        <v>94352507</v>
       </c>
       <c r="B10" t="n">
-        <v>90388</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5851</v>
+        <v>504</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fruktkremla</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Russula decipiens</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Singer) Svrček</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björknäs, SO om, Upl</t>
+          <t>Björknäs, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696037.3541234477</v>
+        <v>695981</v>
       </c>
       <c r="R10" t="n">
-        <v>6637487.782187801</v>
+        <v>6637500</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1751,22 +1653,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Litet bestånd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,34 +1672,33 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>73099195</v>
+        <v>94352508</v>
       </c>
       <c r="B11" t="n">
-        <v>90366</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,39 +1706,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5836</v>
+        <v>504</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björknäs, SO om, Upl</t>
+          <t>Björknäs, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696037.3541234477</v>
+        <v>695970</v>
       </c>
       <c r="R11" t="n">
-        <v>6637487.782187801</v>
+        <v>6637518</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1866,22 +1765,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Större beståndet</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,83 +1784,84 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73112909</v>
+        <v>94381954</v>
       </c>
       <c r="B12" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>150</v>
+        <v>504</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björknäs SO om, Erken, Lohärad, Upl</t>
+          <t>S, Björknäs, Ältan, Edsbro/Lohärad, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696130.3147985887</v>
+        <v>695960</v>
       </c>
       <c r="R12" t="n">
-        <v>6637466.501187766</v>
+        <v>6637514</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1993,27 +1888,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Inventering tillsammans med Kristoffer Stighäll och Birgitta Wasstorp.</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2029,75 +1909,72 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Christoffer Hallbäck</t>
+          <t>Julia Stigenberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Christoffer Hallbäck</t>
+          <t>Julia Stigenberg, Niclas Eklund</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>73120941</v>
+        <v>94381985</v>
       </c>
       <c r="B13" t="n">
-        <v>88896</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>720</v>
+        <v>504</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björknäs, SO om, Upl</t>
+          <t>S, Björknäs, Ältan, Edsbro/Lohärad, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696037.3541234477</v>
+        <v>696002</v>
       </c>
       <c r="R13" t="n">
-        <v>6637487.782187801</v>
+        <v>6637470</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2121,27 +1998,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-20</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I mellersta delen av lokalen, 15 m från landsväg.</t>
+          <t>Strax bortanför huvudlokalen fans tre plantor.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2157,75 +2024,64 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Julia Stigenberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+          <t>Julia Stigenberg, Niclas Eklund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>73120832</v>
+        <v>96200911</v>
       </c>
       <c r="B14" t="n">
-        <v>88906</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5745</v>
+        <v>504</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gyllenfingersvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria brunneicontusa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Björknäs, SO om, Upl</t>
+          <t>Björknäs SO, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696037.3541234477</v>
+        <v>696000</v>
       </c>
       <c r="R14" t="n">
-        <v>6637487.782187801</v>
+        <v>6637525</v>
       </c>
       <c r="S14" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2249,27 +2105,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Minst. Tydligt orangegul. Av "largentii-typ".</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2285,75 +2126,72 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp, Isak Isaksson, Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>73120819</v>
+        <v>118121319</v>
       </c>
       <c r="B15" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5754</v>
+        <v>504</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Björknäs, SO om, Upl</t>
+          <t>Gucku viksjön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696037.3541234477</v>
+        <v>695984</v>
       </c>
       <c r="R15" t="n">
-        <v>6637487.782187801</v>
+        <v>6637498</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2377,27 +2215,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spridd på flera platser.</t>
+          <t>ca 200</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2413,75 +2241,74 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+          <t>Olle Amcoff</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>73120808</v>
+        <v>73112904</v>
       </c>
       <c r="B16" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>150</v>
+        <v>720</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Björknäs, SO om, Upl</t>
+          <t>Björknäs SO om, Erken, Lohärad, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>696037.3541234477</v>
+        <v>696139</v>
       </c>
       <c r="R16" t="n">
-        <v>6637487.782187801</v>
+        <v>6637473</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2508,24 +2335,14 @@
           <t>2018-09-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2018-09-13</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Spridd i området. Flera utmed stigar och stigkors.</t>
+          <t>Inventering tillsammans med Kristoffer Stighäll och Birgitta Wasstorp.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2541,31 +2358,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Christoffer Hallbäck</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+          <t>Christoffer Hallbäck</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>73112904</v>
+        <v>73120941</v>
       </c>
       <c r="B17" t="n">
-        <v>88896</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2588,32 +2400,28 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björknäs SO om, Erken, Lohärad, Upl</t>
+          <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696139.0535116019</v>
+        <v>696037</v>
       </c>
       <c r="R17" t="n">
-        <v>6637473.008019009</v>
+        <v>6637488</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2640,24 +2448,14 @@
           <t>2018-09-13</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2018-09-13</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Inventering tillsammans med Kristoffer Stighäll och Birgitta Wasstorp.</t>
+          <t>I mellersta delen av lokalen, 15 m från landsväg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2673,27 +2471,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Christoffer Hallbäck</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Christoffer Hallbäck</t>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>73112914</v>
+        <v>73099226</v>
       </c>
       <c r="B18" t="n">
-        <v>88953</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2701,51 +2494,47 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5754</v>
+        <v>1988</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Björknäs SO om, Erken, Lohärad, Upl</t>
+          <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696123.2994184983</v>
+        <v>696037</v>
       </c>
       <c r="R18" t="n">
-        <v>6637446.484510424</v>
+        <v>6637488</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2769,27 +2558,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Inventering tillsammans med Kristoffer Stighäll och Birgitta Wasstorp.</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,27 +2579,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Christoffer Hallbäck</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Christoffer Hallbäck</t>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>79970584</v>
+        <v>79970823</v>
       </c>
       <c r="B19" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2833,21 +2602,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222002</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2861,10 +2630,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696011.0557615445</v>
+        <v>696065</v>
       </c>
       <c r="R19" t="n">
-        <v>6637488.911324783</v>
+        <v>6637524</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2894,19 +2663,9 @@
           <t>2019-09-16</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2939,57 +2698,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>79970823</v>
+        <v>96200907</v>
       </c>
       <c r="B20" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2809</v>
+        <v>3286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Björknäs, SO om, Upl</t>
+          <t>Björknäs SO, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696065.2103099811</v>
+        <v>696000</v>
       </c>
       <c r="R20" t="n">
-        <v>6637524.011675387</v>
+        <v>6637525</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3013,27 +2766,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3049,27 +2787,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp, Isak Isaksson, Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>79970723</v>
+        <v>73099330</v>
       </c>
       <c r="B21" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3077,40 +2814,47 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>695984.8074797426</v>
+        <v>696037</v>
       </c>
       <c r="R21" t="n">
-        <v>6637517.748447153</v>
+        <v>6637488</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3134,22 +2878,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3165,61 +2899,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>79970784</v>
+        <v>88230807</v>
       </c>
       <c r="B22" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>150</v>
+        <v>3624</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Pers.) Fayod</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3228,13 +2945,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696074.9540991505</v>
+        <v>696037</v>
       </c>
       <c r="R22" t="n">
-        <v>6637540.142197561</v>
+        <v>6637488</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3258,27 +2975,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3294,49 +2996,48 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>79970562</v>
+        <v>88230874</v>
       </c>
       <c r="B23" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>3674</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3349,13 +3050,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696079.1019061783</v>
+        <v>696037</v>
       </c>
       <c r="R23" t="n">
-        <v>6637413.923859022</v>
+        <v>6637488</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3379,27 +3080,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På torrgran. Kalkbarrskog.</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3415,27 +3101,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>79970789</v>
+        <v>96200938</v>
       </c>
       <c r="B24" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87309</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3443,21 +3128,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>3674</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3466,17 +3151,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Björknäs, SO om, Upl</t>
+          <t>Björknäs SO, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>696074.9540991505</v>
+        <v>696000</v>
       </c>
       <c r="R24" t="n">
-        <v>6637540.142197561</v>
+        <v>6637525</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3500,22 +3185,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3531,53 +3206,60 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp, Isak Isaksson, Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>79970797</v>
+        <v>88230927</v>
       </c>
       <c r="B25" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3586,13 +3268,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>696074.9540991505</v>
+        <v>696037</v>
       </c>
       <c r="R25" t="n">
-        <v>6637540.142197561</v>
+        <v>6637488</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3616,22 +3298,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>I områdets NW del. Lågmark med myskmadra.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3647,53 +3324,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>79969286</v>
+        <v>88230720</v>
       </c>
       <c r="B26" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87375</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>3739</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Persiljespindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius sulfurinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3702,13 +3386,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>696108.8834849475</v>
+        <v>696037</v>
       </c>
       <c r="R26" t="n">
-        <v>6637509.193174792</v>
+        <v>6637488</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3732,22 +3416,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3763,27 +3437,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>79970715</v>
+        <v>88230827</v>
       </c>
       <c r="B27" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3791,21 +3464,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3818,13 +3491,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>695984.8074797426</v>
+        <v>696037</v>
       </c>
       <c r="R27" t="n">
-        <v>6637517.748447153</v>
+        <v>6637488</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3848,22 +3521,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3879,27 +3542,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>79970083</v>
+        <v>88231039</v>
       </c>
       <c r="B28" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90312</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3907,21 +3569,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>4037</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bolmörtsskivling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Entoloma sinuatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Bull.) P.Kumm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3934,13 +3596,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>696108.8834849475</v>
+        <v>696037</v>
       </c>
       <c r="R28" t="n">
-        <v>6637509.193174792</v>
+        <v>6637488</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3964,22 +3626,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-09-27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3995,27 +3647,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>79970628</v>
+        <v>73088664</v>
       </c>
       <c r="B29" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4023,40 +3674,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>696011.0557615445</v>
+        <v>696037</v>
       </c>
       <c r="R29" t="n">
-        <v>6637488.911324783</v>
+        <v>6637488</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4080,22 +3730,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4111,76 +3751,70 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>79969277</v>
+        <v>73088656</v>
       </c>
       <c r="B30" t="n">
-        <v>90642</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>150</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grangråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Boletopsis leucomelaena</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Pers.) Fayod</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>696108.8834849475</v>
+        <v>696037</v>
       </c>
       <c r="R30" t="n">
-        <v>6637509.193174792</v>
+        <v>6637488</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4204,27 +3838,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gammal kalkbarrskog.</t>
+          <t>minst. Väl spridd.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4240,31 +3864,26 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>79970384</v>
+        <v>79970083</v>
       </c>
       <c r="B31" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -4295,10 +3914,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>696073.8273438539</v>
+        <v>696109</v>
       </c>
       <c r="R31" t="n">
-        <v>6637446.892039448</v>
+        <v>6637509</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4328,24 +3947,9 @@
           <t>2019-09-16</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4373,37 +3977,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>88230807</v>
+        <v>79970384</v>
       </c>
       <c r="B32" t="n">
-        <v>85198</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3624</v>
+        <v>4366</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schaeff. : Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4416,13 +4015,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>696037.3541234477</v>
+        <v>696074</v>
       </c>
       <c r="R32" t="n">
-        <v>6637487.782187801</v>
+        <v>6637447</v>
       </c>
       <c r="S32" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4446,22 +4045,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Allmänt förekommande.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4477,53 +4071,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>88230827</v>
+        <v>79970789</v>
       </c>
       <c r="B33" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3762</v>
+        <v>4366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4536,13 +4121,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>696037.3541234477</v>
+        <v>696075</v>
       </c>
       <c r="R33" t="n">
-        <v>6637487.782187801</v>
+        <v>6637540</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4566,22 +4151,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4597,31 +4172,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>88230927</v>
+        <v>73088914</v>
       </c>
       <c r="B34" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4629,21 +4195,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3712</v>
+        <v>4566</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Dofttråding</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Inosperma bongardii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Weinm.) Matheny &amp; Estev-Rav.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4653,21 +4219,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>696037.3541234477</v>
+        <v>696037</v>
       </c>
       <c r="R34" t="n">
-        <v>6637487.782187801</v>
+        <v>6637488</v>
       </c>
       <c r="S34" t="n">
         <v>100</v>
@@ -4694,27 +4259,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>I områdets NW del. Lågmark med myskmadra.</t>
+          <t>Områdets N del. I svacka. Rik markväxtlighet med kransmossa, blåsippa och harsyra.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4735,53 +4290,44 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>88230720</v>
+        <v>73088925</v>
       </c>
       <c r="B35" t="n">
-        <v>85301</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3739</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Persiljespindling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cortinarius sulfurinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Quél.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4790,17 +4336,16 @@
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>696037.3541234477</v>
+        <v>696037</v>
       </c>
       <c r="R35" t="n">
-        <v>6637487.782187801</v>
+        <v>6637488</v>
       </c>
       <c r="S35" t="n">
         <v>100</v>
@@ -4827,22 +4372,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Minst. Väl spridd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4863,26 +4403,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>88231039</v>
+        <v>79970723</v>
       </c>
       <c r="B36" t="n">
-        <v>86011</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4890,21 +4421,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4037</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bolmörtsskivling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Entoloma sinuatum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Bull.) P.Kumm.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4917,13 +4448,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>696037.3541234477</v>
+        <v>695985</v>
       </c>
       <c r="R36" t="n">
-        <v>6637487.782187801</v>
+        <v>6637518</v>
       </c>
       <c r="S36" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4947,22 +4478,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4978,69 +4499,67 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>88231053</v>
+        <v>73120832</v>
       </c>
       <c r="B37" t="n">
-        <v>88943</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91398</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5747</v>
+        <v>5745</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Gyllenfingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria brunneicontusa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Christian</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>696037.3541234477</v>
+        <v>696037</v>
       </c>
       <c r="R37" t="n">
-        <v>6637487.782187801</v>
+        <v>6637488</v>
       </c>
       <c r="S37" t="n">
         <v>100</v>
@@ -5067,27 +4586,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2020-09-27</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Mattias Anderssons kommentar: "Den har gula toppar och nedanför laxrosa med en tydlig doft av läder eller saffran. Sporerna är ganska stora, jag mätte upp dem till 12µm.".</t>
+          <t>Minst. Tydligt orangegul. Av "largentii-typ".</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5101,16 +4610,6 @@
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>Mattias Andersson</t>
-        </is>
-      </c>
-      <c r="AV37" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
       <c r="AW37" t="inlineStr">
         <is>
           <t>Kristoffer Stighäll</t>
@@ -5118,48 +4617,39 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>88230874</v>
+        <v>88231053</v>
       </c>
       <c r="B38" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91435</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3674</v>
+        <v>5747</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5172,10 +4662,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>696037.3541234477</v>
+        <v>696037</v>
       </c>
       <c r="R38" t="n">
-        <v>6637487.782187801</v>
+        <v>6637488</v>
       </c>
       <c r="S38" t="n">
         <v>100</v>
@@ -5205,19 +4695,14 @@
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2020-09-27</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Mattias Anderssons kommentar: "Den har gula toppar och nedanför laxrosa med en tydlig doft av läder eller saffran. Sporerna är ganska stora, jag mätte upp dem till 12µm.".</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5231,6 +4716,16 @@
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>Mattias Andersson</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
       <c r="AW38" t="inlineStr">
         <is>
           <t>Kristoffer Stighäll</t>
@@ -5238,7 +4733,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll, Birgitta Wasstorp, Mattias Andersson, Isak Isaksson, Joakim Ekman</t>
+          <t>Isak Isaksson, Mattias Andersson, Birgitta Wasstorp, Kristoffer Stighäll, Joakim Ekman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -5249,58 +4744,62 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>94352509</v>
+        <v>73112914</v>
       </c>
       <c r="B39" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221235</v>
+        <v>5754</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Björknäs, Upl</t>
+          <t>Björknäs SO om, Erken, Lohärad, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>696003.8784692119</v>
+        <v>696123</v>
       </c>
       <c r="R39" t="n">
-        <v>6637491.050791974</v>
+        <v>6637446</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5324,22 +4823,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Inventering tillsammans med Kristoffer Stighäll och Birgitta Wasstorp.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5348,79 +4842,77 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Christoffer Hallbäck</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Christoffer Hallbäck</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>96200938</v>
+        <v>73120819</v>
       </c>
       <c r="B40" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3674</v>
+        <v>5754</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Björknäs SO, Upl</t>
+          <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>695999.5579260995</v>
+        <v>696037</v>
       </c>
       <c r="R40" t="n">
-        <v>6637525.076161684</v>
+        <v>6637488</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5444,22 +4936,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-13</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spridd på flera platser.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5475,72 +4962,62 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isak Isaksson, Birgitta Wasstorp, Kristoffer Stighäll</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>96200907</v>
+        <v>73099195</v>
       </c>
       <c r="B41" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92928</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3286</v>
+        <v>5836</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Björknäs SO, Upl</t>
+          <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>695999.5579260995</v>
+        <v>696037</v>
       </c>
       <c r="R41" t="n">
-        <v>6637525.076161684</v>
+        <v>6637488</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5564,22 +5041,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5595,83 +5062,62 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isak Isaksson, Birgitta Wasstorp, Kristoffer Stighäll</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>16882754</v>
+        <v>73099153</v>
       </c>
       <c r="B42" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>504</v>
+        <v>5851</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fruktkremla</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Russula decipiens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Singer) Svrček</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Björknäs (*gk* /stjälk/), Upl</t>
+          <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>695966.3745349223</v>
+        <v>696037</v>
       </c>
       <c r="R42" t="n">
-        <v>6637522.819468501</v>
+        <v>6637488</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5693,34 +5139,14 @@
           <t>Lohärad</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>AB-Nor-0634-biogeo</t>
-        </is>
-      </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2014-06-22</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2014-06-22</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>9 grupper med totalt 77 blommor</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5729,80 +5155,77 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson, Ebbe Zachrisson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>94352507</v>
+        <v>73088665</v>
       </c>
       <c r="B43" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>504</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Björknäs, Upl</t>
+          <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>695980.651343578</v>
+        <v>696037</v>
       </c>
       <c r="R43" t="n">
-        <v>6637500.90582502</v>
+        <v>6637488</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5826,27 +5249,17 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-06</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Litet bestånd.</t>
+          <t>minst. Väl spridd.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5855,76 +5268,70 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Kristoffer Stighäll, Birgitta Wasstorp</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>6764842</v>
+        <v>79969286</v>
       </c>
       <c r="B44" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>504</v>
+        <v>5964</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Björklund 300 m V (*gk* /stjälk/), Upl</t>
+          <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>696092.9802523537</v>
+        <v>696109</v>
       </c>
       <c r="R44" t="n">
-        <v>6637409.116173979</v>
+        <v>6637509</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5946,34 +5353,14 @@
           <t>Lohärad</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>AB-Nor-0635</t>
-        </is>
-      </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>1995-10-26</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>1995-10-26</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Objekt 15:1</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5982,86 +5369,67 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>AB-län Floraväktarna</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Stefan Eklund</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>53976133</v>
+        <v>79970628</v>
       </c>
       <c r="B45" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>504</v>
+        <v>5964</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Björknäs SO, Upl</t>
+          <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>695965.5548693982</v>
+        <v>696011</v>
       </c>
       <c r="R45" t="n">
-        <v>6637509.679240229</v>
+        <v>6637489</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6088,27 +5456,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2015-06-15</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ett bestånd ca 4 x 2 m.</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6117,66 +5470,56 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Örtrik gammal granskog med stort lövinslag.</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Magnus Bergström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>79970656</v>
+        <v>79970715</v>
       </c>
       <c r="B46" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>504</v>
+        <v>5964</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6184,10 +5527,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>695974.9561282761</v>
+        <v>695985</v>
       </c>
       <c r="R46" t="n">
-        <v>6637513.198215585</v>
+        <v>6637518</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6217,24 +5560,9 @@
           <t>2019-09-16</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2019-09-16</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Många exemplar på en yta av ca 2x3m. Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6262,66 +5590,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>94381954</v>
+        <v>79970797</v>
       </c>
       <c r="B47" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>504</v>
+        <v>5964</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>S, Björknäs, Ältan, Edsbro/Lohärad, Upl</t>
+          <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>695960.7608944543</v>
+        <v>696075</v>
       </c>
       <c r="R47" t="n">
-        <v>6637514.463304172</v>
+        <v>6637540</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6348,22 +5658,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6379,44 +5679,39 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Julia Stigenberg</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Julia Stigenberg, Niclas Eklund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>94352508</v>
+        <v>53976134</v>
       </c>
       <c r="B48" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>504</v>
+        <v>219711</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6424,25 +5719,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Björknäs, Upl</t>
+          <t>Björknäs SO, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>695970.6918605741</v>
+        <v>696032</v>
       </c>
       <c r="R48" t="n">
-        <v>6637517.506516664</v>
+        <v>6637537</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6466,27 +5770,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-06-15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Större beståndet</t>
+          <t>2015-06-15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6500,83 +5789,71 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Örtrik granskog</t>
+          <t>Örtrik gammal granskog med stort lövinslag.</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Magnus Bergström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>94381985</v>
+        <v>94352509</v>
       </c>
       <c r="B49" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>504</v>
+        <v>221235</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>S, Björknäs, Ältan, Edsbro/Lohärad, Upl</t>
+          <t>Björknäs, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>696001.9474381353</v>
+        <v>696004</v>
       </c>
       <c r="R49" t="n">
-        <v>6637470.295697819</v>
+        <v>6637491</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6600,27 +5877,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2021-06-20</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Strax bortanför huvudlokalen fans tre plantor.</t>
+          <t>2021-06-19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6629,34 +5891,33 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Julia Stigenberg</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Julia Stigenberg, Niclas Eklund</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>96200911</v>
+        <v>79970584</v>
       </c>
       <c r="B50" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6664,16 +5925,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>504</v>
+        <v>222002</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -6688,17 +5949,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Björknäs SO, Upl</t>
+          <t>Björknäs, SO om, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>695999.5579260995</v>
+        <v>696011</v>
       </c>
       <c r="R50" t="n">
-        <v>6637525.076161684</v>
+        <v>6637489</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6722,22 +5983,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-16</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6753,135 +6009,15 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk, Isak Isaksson, Birgitta Wasstorp, Kristoffer Stighäll</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>118121319</v>
-      </c>
-      <c r="B51" t="n">
-        <v>97752</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>504</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Guckusko</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Cypripedium calceolus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Gucku viksjön, Upl</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>695984</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6637498</v>
-      </c>
-      <c r="S51" t="n">
-        <v>25</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Lohärad</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>ca 200</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Olle Amcoff</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Olle Amcoff</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30156-2022 artfynd.xlsx
+++ b/artfynd/A 30156-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73112909</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73120808</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79969277</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79970784</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6759043</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6764842</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1473,6 +1508,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53976133</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1580,6 +1620,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79970656</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1692,6 +1737,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94352507</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1804,6 +1854,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94352508</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1918,6 +1973,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94381954</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2033,6 +2093,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94381985</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2139,6 +2204,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96200911</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2250,6 +2320,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118121319</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2367,6 +2442,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73112904</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2480,6 +2560,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73120941</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2588,6 +2673,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73099226</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2695,6 +2785,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79970823</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2800,6 +2895,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96200907</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2908,6 +3008,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73099330</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3009,6 +3114,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88230807</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3114,6 +3224,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88230874</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3219,6 +3334,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96200938</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3337,6 +3457,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88230927</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3448,6 +3573,11 @@
       <c r="AY26" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88230720</t>
         </is>
       </c>
     </row>
@@ -3555,6 +3685,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88230827</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3660,6 +3795,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88231039</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3760,6 +3900,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73088664</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3873,6 +4018,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73088656</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3974,6 +4124,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79970083</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4080,6 +4235,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79970384</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4181,6 +4341,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79970789</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4294,6 +4459,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73088914</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4407,6 +4577,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73088925</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4508,6 +4683,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79970723</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4621,6 +4801,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73120832</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4741,6 +4926,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88231053</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4858,6 +5048,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73112914</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4971,6 +5166,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73120819</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5071,6 +5271,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73099195</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5171,6 +5376,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73099153</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5284,6 +5494,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73088665</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5385,6 +5600,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79969286</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5486,6 +5706,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79970628</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5587,6 +5812,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79970715</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5688,6 +5918,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79970797</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5804,6 +6039,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53976134</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5911,6 +6151,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94352509</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6018,8 +6263,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79970584</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>